--- a/2026/GAEBELER 1949/Febrero/gaebeler.xlsx
+++ b/2026/GAEBELER 1949/Febrero/gaebeler.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GAEBELER 1949\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945DE6FB-E62A-4997-898F-528C8E5470E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E9FF1B-6146-4D13-B18B-F56CCE5BF7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -245,9 +245,6 @@
     <t>TELEFONO: 11-5320-2676</t>
   </si>
   <si>
-    <t>LUNES A VIERNES 10 A 16HS</t>
-  </si>
-  <si>
     <t xml:space="preserve">EDESUR </t>
   </si>
   <si>
@@ -330,6 +327,9 @@
   </si>
   <si>
     <t>¡POR FAVOR RESPETAR LOS CENTAVOS AL ABONAR!</t>
+  </si>
+  <si>
+    <t>LUNES A VIERNES 10 A 15HS</t>
   </si>
 </sst>
 </file>
@@ -344,10 +344,10 @@
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -1118,7 +1118,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1306,86 +1306,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1400,7 +1329,7 @@
     <xf numFmtId="0" fontId="26" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="26" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="26" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1421,10 +1350,10 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="27" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="27" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1441,43 +1370,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="27" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="27" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="43" fontId="12" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="29" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="29" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="27" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1493,26 +1413,103 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="22" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1881,20 +1878,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M90"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="15"/>
       <c r="B1" s="60" t="s">
         <v>71</v>
@@ -1903,94 +1900,94 @@
       <c r="D1" s="60"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
-      <c r="B2" s="217" t="s">
+      <c r="B2" s="194" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="219"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="218" t="s">
+      <c r="B3" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="216"/>
-      <c r="D3" s="216"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
-      <c r="B4" s="216" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="216"/>
-      <c r="D4" s="216"/>
+      <c r="B4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="220" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="221"/>
-      <c r="C5" s="221"/>
-      <c r="D5" s="221" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" s="222"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="132" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="132"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="131" t="s">
+    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="189" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="190"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="190" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="191"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="201" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="201"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="201"/>
+      <c r="C8" s="201"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="201"/>
+      <c r="C9" s="201"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="200" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="131"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="131"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="131"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-    </row>
-    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="131"/>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="200"/>
+      <c r="C12" s="200"/>
+      <c r="D12" s="200"/>
+      <c r="E12" s="200"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="200"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="200"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="200"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="200"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+    </row>
+    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="200"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>5</v>
       </c>
@@ -1999,65 +1996,65 @@
       <c r="D19" s="9"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="114"/>
       <c r="C20" s="114"/>
       <c r="D20" s="115"/>
       <c r="E20" s="116"/>
     </row>
-    <row r="21" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="125" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="126"/>
+    <row r="21" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="192" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="193"/>
       <c r="C21" s="5"/>
       <c r="D21" s="117">
         <v>52745</v>
       </c>
       <c r="E21" s="120"/>
     </row>
-    <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="125" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="126"/>
+    <row r="22" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="192" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="193"/>
       <c r="C22" s="5"/>
       <c r="D22" s="117">
         <v>52745</v>
       </c>
       <c r="E22" s="120"/>
     </row>
-    <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="125" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="126"/>
+    <row r="23" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="193"/>
       <c r="C23" s="5"/>
       <c r="D23" s="117">
         <v>52745</v>
       </c>
       <c r="E23" s="120"/>
     </row>
-    <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="125" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="126"/>
+    <row r="24" spans="1:5" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="192" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="193"/>
       <c r="C24" s="5"/>
       <c r="D24" s="117">
         <v>52745</v>
       </c>
       <c r="E24" s="120"/>
     </row>
-    <row r="25" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="124" t="s">
         <v>91</v>
-      </c>
-      <c r="B25" s="124" t="s">
-        <v>92</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="117">
@@ -2065,12 +2062,12 @@
       </c>
       <c r="E25" s="120"/>
     </row>
-    <row r="26" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="124" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="117">
@@ -2078,45 +2075,45 @@
       </c>
       <c r="E26" s="120"/>
     </row>
-    <row r="27" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="213" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="214" t="s">
+    <row r="27" spans="1:5" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="185" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="186" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="118"/>
+      <c r="D27" s="184">
+        <v>33346.25</v>
+      </c>
+      <c r="E27" s="120"/>
+    </row>
+    <row r="28" spans="1:5" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="185" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="212">
-        <v>33346.25</v>
-      </c>
-      <c r="E27" s="120"/>
-    </row>
-    <row r="28" spans="1:5" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="213" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="124" t="s">
-        <v>95</v>
-      </c>
       <c r="C28" s="118"/>
-      <c r="D28" s="212">
+      <c r="D28" s="184">
         <v>42819.86</v>
       </c>
       <c r="E28" s="120"/>
     </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="26"/>
       <c r="C29" s="26"/>
-      <c r="D29" s="211"/>
+      <c r="D29" s="183"/>
       <c r="E29" s="113">
         <f>SUM(D21:D28)</f>
         <v>345093.76999999996</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>4</v>
       </c>
@@ -2128,14 +2125,14 @@
         <v>345093.76999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="78"/>
       <c r="E31" s="84"/>
     </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="27" t="s">
         <v>34</v>
       </c>
@@ -2144,13 +2141,13 @@
       <c r="D32" s="85"/>
       <c r="E32" s="86"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1"/>
       <c r="D33" s="87"/>
       <c r="E33" s="88"/>
       <c r="F33" s="39"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>7</v>
       </c>
@@ -2164,15 +2161,15 @@
       <c r="F34" s="112"/>
       <c r="G34" s="39"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D35" s="87"/>
       <c r="E35" s="87"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D36" s="87"/>
       <c r="E36" s="87"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>30</v>
       </c>
@@ -2181,35 +2178,35 @@
       <c r="D37" s="91"/>
       <c r="E37" s="92"/>
     </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="125"/>
-      <c r="B38" s="126"/>
+    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="192"/>
+      <c r="B38" s="193"/>
       <c r="C38" s="5"/>
       <c r="D38" s="101"/>
       <c r="E38" s="79"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="125"/>
-      <c r="B39" s="126"/>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="192"/>
+      <c r="B39" s="193"/>
       <c r="C39" s="5"/>
       <c r="D39" s="81"/>
       <c r="E39" s="79"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="129"/>
-      <c r="B40" s="130"/>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="198"/>
+      <c r="B40" s="199"/>
       <c r="C40" s="5"/>
       <c r="D40" s="81"/>
       <c r="E40" s="79"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="80"/>
       <c r="B41" s="82"/>
       <c r="C41" s="5"/>
       <c r="D41" s="81"/>
       <c r="E41" s="79"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="45"/>
       <c r="B42" s="44"/>
       <c r="C42" s="44"/>
@@ -2219,9 +2216,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
         <v>10</v>
       </c>
@@ -2230,8 +2227,8 @@
       <c r="D45" s="28"/>
       <c r="E45" s="77"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>11</v>
       </c>
@@ -2243,8 +2240,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="75" t="s">
         <v>8</v>
       </c>
@@ -2253,7 +2250,7 @@
         <v>345093.76999999996</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="75" t="s">
         <v>9</v>
       </c>
@@ -2262,7 +2259,7 @@
         <v>345093.76999999996</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="75" t="s">
         <v>12</v>
       </c>
@@ -2271,7 +2268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="75" t="s">
         <v>26</v>
       </c>
@@ -2280,44 +2277,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="127"/>
-      <c r="B55" s="127"/>
-      <c r="C55" s="127"/>
-      <c r="D55" s="127"/>
-      <c r="E55" s="127"/>
-    </row>
-    <row r="56" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="127"/>
-      <c r="B56" s="127"/>
-      <c r="C56" s="127"/>
-      <c r="D56" s="127"/>
-      <c r="E56" s="127"/>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="127"/>
-      <c r="B57" s="127"/>
-      <c r="C57" s="127"/>
-      <c r="D57" s="127"/>
-      <c r="E57" s="127"/>
-    </row>
-    <row r="59" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="196"/>
+      <c r="B55" s="196"/>
+      <c r="C55" s="196"/>
+      <c r="D55" s="196"/>
+      <c r="E55" s="196"/>
+    </row>
+    <row r="56" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="196"/>
+      <c r="B56" s="196"/>
+      <c r="C56" s="196"/>
+      <c r="D56" s="196"/>
+      <c r="E56" s="196"/>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="196"/>
+      <c r="B57" s="196"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+    </row>
+    <row r="59" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B59" s="98"/>
       <c r="C59" s="21"/>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="30"/>
       <c r="B60" s="52">
         <v>0</v>
       </c>
       <c r="C60" s="23"/>
     </row>
-    <row r="61" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>2</v>
       </c>
@@ -2327,14 +2324,14 @@
       </c>
       <c r="C61" s="21"/>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22"/>
       <c r="B62" s="36">
         <v>0</v>
       </c>
       <c r="C62" s="21"/>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>27</v>
       </c>
@@ -2344,19 +2341,19 @@
       </c>
       <c r="C63" s="21"/>
     </row>
-    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="25"/>
       <c r="B64" s="43"/>
       <c r="C64" s="21"/>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="97" t="s">
         <v>31</v>
       </c>
       <c r="B65" s="43"/>
       <c r="C65" s="21"/>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
         <v>13</v>
       </c>
@@ -2366,7 +2363,7 @@
       </c>
       <c r="C66" s="21"/>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="25" t="s">
         <v>14</v>
       </c>
@@ -2376,7 +2373,7 @@
       </c>
       <c r="C67" s="21"/>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
         <v>4</v>
       </c>
@@ -2387,31 +2384,31 @@
       <c r="C68" s="24"/>
       <c r="D68" s="39"/>
     </row>
-    <row r="69" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="37"/>
       <c r="C69" s="24"/>
       <c r="D69" s="39"/>
       <c r="E69" s="99"/>
       <c r="F69" s="100"/>
     </row>
-    <row r="70" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="38"/>
       <c r="C70" s="24"/>
     </row>
-    <row r="71" spans="1:6" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71"/>
       <c r="B71" s="37"/>
       <c r="C71" s="33"/>
     </row>
-    <row r="72" spans="1:6" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" s="34" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="215"/>
+      <c r="B72" s="187"/>
       <c r="C72" s="33"/>
       <c r="D72" s="42"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>35</v>
       </c>
@@ -2420,7 +2417,7 @@
         <v>-345093.76999999996</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="48" t="s">
         <v>36</v>
       </c>
@@ -2429,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="s">
         <v>41</v>
       </c>
@@ -2438,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="48" t="s">
         <v>37</v>
       </c>
@@ -2447,13 +2444,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="110" t="s">
         <v>38</v>
       </c>
       <c r="B77" s="111"/>
     </row>
-    <row r="78" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="106" t="s">
         <v>32</v>
       </c>
@@ -2462,24 +2459,24 @@
         <v>-345093.76999999996</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="104"/>
       <c r="B79" s="104"/>
     </row>
-    <row r="80" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="128" t="s">
+    <row r="80" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="197" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="128"/>
-      <c r="C81" s="128"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="128"/>
-      <c r="B82" s="128"/>
-      <c r="C82" s="128"/>
-    </row>
-    <row r="83" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="197"/>
+      <c r="C81" s="197"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="197"/>
+      <c r="B82" s="197"/>
+      <c r="C82" s="197"/>
+    </row>
+    <row r="83" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="94"/>
       <c r="B83" s="32"/>
       <c r="C83" s="32">
@@ -2487,13 +2484,13 @@
       </c>
       <c r="E83" s="112"/>
     </row>
-    <row r="84" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="94"/>
       <c r="B84" s="96"/>
       <c r="C84" s="93"/>
       <c r="D84" s="112"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="40" t="s">
         <v>4</v>
       </c>
@@ -2503,36 +2500,36 @@
       </c>
       <c r="C85" s="41"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M86" s="8"/>
     </row>
-    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="127"/>
-      <c r="B87" s="127"/>
-      <c r="C87" s="127"/>
-      <c r="D87" s="127"/>
-      <c r="E87" s="127"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="127"/>
-      <c r="B88" s="127"/>
-      <c r="C88" s="127"/>
-      <c r="D88" s="127"/>
-      <c r="E88" s="127"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="127"/>
-      <c r="B89" s="127"/>
-      <c r="C89" s="127"/>
-      <c r="D89" s="127"/>
-      <c r="E89" s="127"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="127"/>
-      <c r="B90" s="127"/>
-      <c r="C90" s="127"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="127"/>
+    <row r="87" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="196"/>
+      <c r="B87" s="196"/>
+      <c r="C87" s="196"/>
+      <c r="D87" s="196"/>
+      <c r="E87" s="196"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="196"/>
+      <c r="B88" s="196"/>
+      <c r="C88" s="196"/>
+      <c r="D88" s="196"/>
+      <c r="E88" s="196"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="196"/>
+      <c r="B89" s="196"/>
+      <c r="C89" s="196"/>
+      <c r="D89" s="196"/>
+      <c r="E89" s="196"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="196"/>
+      <c r="B90" s="196"/>
+      <c r="C90" s="196"/>
+      <c r="D90" s="196"/>
+      <c r="E90" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2559,59 +2556,59 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="0.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="224" t="str">
+      <c r="B1" s="17" t="str">
         <f>RESUMEN!B4</f>
         <v>TRANSFERIR A  : carolina.rc.adm - CVU: 0000003100054616492658</v>
       </c>
       <c r="C1" s="17"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="223"/>
-      <c r="K1" s="223"/>
-      <c r="L1" s="223"/>
-      <c r="M1" s="223"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="225" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="225"/>
-      <c r="D2" s="225"/>
-      <c r="E2" s="225"/>
-      <c r="F2" s="225"/>
-      <c r="G2" s="225"/>
-      <c r="H2" s="225"/>
+      <c r="B2" s="216" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="216"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="216"/>
+      <c r="F2" s="216"/>
+      <c r="G2" s="216"/>
+      <c r="H2" s="216"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
@@ -2625,15 +2622,15 @@
       <c r="O2" s="49"/>
       <c r="P2" s="19"/>
     </row>
-    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="226"/>
-      <c r="C3" s="226"/>
-      <c r="D3" s="226"/>
-      <c r="E3" s="226"/>
-      <c r="F3" s="226"/>
-      <c r="G3" s="226"/>
-      <c r="H3" s="226"/>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="217"/>
+      <c r="H3" s="217"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -2642,75 +2639,75 @@
       <c r="N3" s="50"/>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="137" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="204" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="204" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="137" t="s">
+      <c r="D4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="133" t="s">
+      <c r="E4" s="207" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="137" t="s">
+      <c r="F4" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="137" t="s">
+      <c r="G4" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="139" t="s">
+      <c r="H4" s="211" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="133" t="s">
+      <c r="I4" s="207" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="133" t="s">
+      <c r="J4" s="207" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="133" t="s">
+      <c r="K4" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="142" t="s">
+      <c r="L4" s="214" t="s">
         <v>39</v>
       </c>
       <c r="M4" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="135" t="s">
+      <c r="N4" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="144" t="s">
+      <c r="O4" s="202" t="s">
         <v>23</v>
       </c>
       <c r="R4" s="39"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="138"/>
-      <c r="B5" s="138"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="138"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="141"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="143"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="206"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="205"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="205"/>
+      <c r="H5" s="212"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="215"/>
       <c r="M5" s="54" t="str">
         <f>RESUMEN!B7</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="N5" s="136"/>
-      <c r="O5" s="145"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N5" s="210"/>
+      <c r="O5" s="203"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="57" t="s">
         <v>47</v>
       </c>
@@ -2763,7 +2760,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="57" t="s">
         <v>48</v>
       </c>
@@ -2818,7 +2815,7 @@
       </c>
       <c r="Q7" s="39"/>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="57" t="s">
         <v>50</v>
       </c>
@@ -2872,7 +2869,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="57" t="s">
         <v>51</v>
       </c>
@@ -2927,7 +2924,7 @@
       </c>
       <c r="R9" s="39"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="57" t="s">
         <v>52</v>
       </c>
@@ -2982,7 +2979,7 @@
       </c>
       <c r="R10" s="39"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="57" t="s">
         <v>53</v>
       </c>
@@ -3036,7 +3033,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="57" t="s">
         <v>54</v>
       </c>
@@ -3090,7 +3087,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="57" t="s">
         <v>56</v>
       </c>
@@ -3144,7 +3141,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="57" t="s">
         <v>57</v>
       </c>
@@ -3198,7 +3195,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="57" t="s">
         <v>58</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="57" t="s">
         <v>64</v>
       </c>
@@ -3306,7 +3303,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="57" t="s">
         <v>65</v>
       </c>
@@ -3360,7 +3357,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="57" t="s">
         <v>63</v>
       </c>
@@ -3409,7 +3406,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="58"/>
@@ -3445,7 +3442,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>66</v>
       </c>
@@ -3494,7 +3491,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>67</v>
       </c>
@@ -3543,7 +3540,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>68</v>
       </c>
@@ -3592,7 +3589,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>69</v>
       </c>
@@ -3641,7 +3638,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="57" t="s">
         <v>70</v>
       </c>
@@ -3695,7 +3692,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="71"/>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
@@ -3748,71 +3745,72 @@
         <v>355452.76</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
       <c r="D26" s="122"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="127" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="127"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="127"/>
-      <c r="K27" s="127"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="127"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="127"/>
-      <c r="C28" s="127"/>
-      <c r="D28" s="127"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="127"/>
-      <c r="J28" s="127"/>
-      <c r="K28" s="127"/>
-      <c r="L28" s="127"/>
-      <c r="M28" s="127"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="127"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="127"/>
-    </row>
-    <row r="30" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="127"/>
-      <c r="C30" s="127"/>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127"/>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127"/>
-      <c r="H30" s="127"/>
-      <c r="I30" s="127"/>
-      <c r="J30" s="127"/>
-      <c r="K30" s="127"/>
-      <c r="L30" s="127"/>
-      <c r="M30" s="127"/>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B27" s="196" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="196"/>
+      <c r="D27" s="196"/>
+      <c r="E27" s="196"/>
+      <c r="F27" s="196"/>
+      <c r="G27" s="196"/>
+      <c r="H27" s="196"/>
+      <c r="I27" s="196"/>
+      <c r="J27" s="196"/>
+      <c r="K27" s="196"/>
+      <c r="L27" s="196"/>
+      <c r="M27" s="196"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B28" s="196"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="196"/>
+      <c r="G28" s="196"/>
+      <c r="H28" s="196"/>
+      <c r="I28" s="196"/>
+      <c r="J28" s="196"/>
+      <c r="K28" s="196"/>
+      <c r="L28" s="196"/>
+      <c r="M28" s="196"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" s="196"/>
+      <c r="C29" s="196"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="196"/>
+      <c r="G29" s="196"/>
+      <c r="H29" s="196"/>
+      <c r="I29" s="196"/>
+      <c r="J29" s="196"/>
+      <c r="K29" s="196"/>
+      <c r="L29" s="196"/>
+      <c r="M29" s="196"/>
+    </row>
+    <row r="30" spans="1:16" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="196"/>
+      <c r="C30" s="196"/>
+      <c r="D30" s="196"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="196"/>
+      <c r="G30" s="196"/>
+      <c r="H30" s="196"/>
+      <c r="I30" s="196"/>
+      <c r="J30" s="196"/>
+      <c r="K30" s="196"/>
+      <c r="L30" s="196"/>
+      <c r="M30" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:H3"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="B27:M30"/>
     <mergeCell ref="C4:C5"/>
@@ -3828,7 +3826,6 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
-    <mergeCell ref="B2:H3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3838,1126 +3835,1126 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642D1833-D35F-45AC-9D7A-9C6C07C828FD}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="218" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="220"/>
+    </row>
+    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="130"/>
+      <c r="B2" s="130" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="131"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="128"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="130"/>
+      <c r="B3" s="129" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="223">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="223"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="221">
+        <f>C2-I24</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="221"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="128"/>
+    </row>
+    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="148"/>
-      <c r="H1" s="148"/>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="149"/>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155" t="s">
+      <c r="B4" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="150"/>
-      <c r="L2" s="150"/>
-      <c r="M2" s="150"/>
-      <c r="N2" s="153"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="155"/>
-      <c r="B3" s="154" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="206">
-        <v>100000</v>
-      </c>
-      <c r="D3" s="206"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="152"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="204">
-        <f>C2-I24</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="204"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="153"/>
-    </row>
-    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="161" t="s">
+      <c r="C4" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="161" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="162" t="s">
+      <c r="D4" s="138" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="163" t="s">
+      <c r="E4" s="138" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="163" t="s">
+      <c r="F4" s="139" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="164" t="s">
+      <c r="G4" s="139" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="164" t="s">
+      <c r="H4" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="165" t="s">
+      <c r="I4" s="141" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="179" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="166" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="207" t="s">
+      <c r="K4" s="179" t="s">
+        <v>80</v>
+      </c>
+      <c r="L4" s="142" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="139" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="207" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4" s="167" t="s">
-        <v>80</v>
-      </c>
-      <c r="M4" s="164" t="s">
-        <v>82</v>
-      </c>
-      <c r="N4" s="153"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="168">
+      <c r="N4" s="128"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="143">
         <v>1</v>
       </c>
-      <c r="B5" s="169">
+      <c r="B5" s="144">
         <v>1</v>
       </c>
-      <c r="C5" s="170" t="str">
+      <c r="C5" s="145" t="str">
         <f>PRORRATEO!A6</f>
         <v>1A</v>
       </c>
-      <c r="D5" s="171" t="str">
+      <c r="D5" s="146" t="str">
         <f>PRORRATEO!B6</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E5" s="172">
+      <c r="E5" s="147">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F5" s="173">
-        <v>0</v>
-      </c>
-      <c r="G5" s="173">
-        <v>0</v>
-      </c>
-      <c r="H5" s="174">
+      <c r="F5" s="148">
+        <v>0</v>
+      </c>
+      <c r="G5" s="148">
+        <v>0</v>
+      </c>
+      <c r="H5" s="149">
         <f>G5-F5</f>
         <v>0</v>
       </c>
-      <c r="I5" s="175">
+      <c r="I5" s="150">
         <f>L5*93.787</f>
         <v>0</v>
       </c>
-      <c r="J5" s="175">
+      <c r="J5" s="150">
         <f>J3*E5%</f>
         <v>0</v>
       </c>
-      <c r="K5" s="209">
-        <f>K$3*E5/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="176">
-        <f>G5-F5</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="174">
+      <c r="K5" s="181">
+        <f t="shared" ref="K5:K23" si="0">K$3*E5/Q$7</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="151">
+        <f t="shared" ref="L5:L21" si="1">G5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="149">
         <f>I5+K5</f>
         <v>0</v>
       </c>
-      <c r="N5" s="153"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="178">
+      <c r="N5" s="128"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="153">
         <v>2</v>
       </c>
-      <c r="B6" s="179">
+      <c r="B6" s="154">
         <v>2</v>
       </c>
-      <c r="C6" s="170" t="str">
+      <c r="C6" s="145" t="str">
         <f>PRORRATEO!A7</f>
         <v>1B</v>
       </c>
-      <c r="D6" s="171" t="str">
+      <c r="D6" s="146" t="str">
         <f>PRORRATEO!B7</f>
         <v>D' Andrea Patricia Daniela</v>
       </c>
-      <c r="E6" s="172">
+      <c r="E6" s="147">
         <v>5.09</v>
       </c>
-      <c r="F6" s="173">
-        <v>0</v>
-      </c>
-      <c r="G6" s="173">
-        <v>0</v>
-      </c>
-      <c r="H6" s="174">
-        <f t="shared" ref="H6:H22" si="0">G6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="175">
-        <f t="shared" ref="I6:I21" si="1">L6*93.787</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="175">
+      <c r="F6" s="148">
+        <v>0</v>
+      </c>
+      <c r="G6" s="148">
+        <v>0</v>
+      </c>
+      <c r="H6" s="149">
+        <f t="shared" ref="H6:H22" si="2">G6-F6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="150">
+        <f t="shared" ref="I6:I21" si="3">L6*93.787</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="150">
         <f>J3*E6%</f>
         <v>0</v>
       </c>
-      <c r="K6" s="209">
-        <f>K$3*E6/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="176">
-        <f>G6-F6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="174">
-        <f t="shared" ref="M6:M20" si="2">I6+K6</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="153"/>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="168">
+      <c r="K6" s="181">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="149">
+        <f t="shared" ref="M6:M20" si="4">I6+K6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="128"/>
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="143">
         <v>3</v>
       </c>
-      <c r="B7" s="179">
+      <c r="B7" s="154">
         <v>3</v>
       </c>
-      <c r="C7" s="170" t="str">
+      <c r="C7" s="145" t="str">
         <f>PRORRATEO!A8</f>
         <v>1C</v>
       </c>
-      <c r="D7" s="171" t="str">
+      <c r="D7" s="146" t="str">
         <f>PRORRATEO!B8</f>
         <v>Arroyo Aldana</v>
       </c>
-      <c r="E7" s="172">
+      <c r="E7" s="147">
         <v>5.04</v>
       </c>
-      <c r="F7" s="173">
-        <v>0</v>
-      </c>
-      <c r="G7" s="173">
-        <v>0</v>
-      </c>
-      <c r="H7" s="174">
+      <c r="F7" s="148">
+        <v>0</v>
+      </c>
+      <c r="G7" s="148">
+        <v>0</v>
+      </c>
+      <c r="H7" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="150">
+        <f>J3*E7%</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="175">
+      <c r="L7" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="175">
-        <f>J3*E7%</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="209">
-        <f>K$3*E7/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="176">
-        <f>G7-F7</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="153"/>
+      <c r="M7" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="128"/>
       <c r="Q7">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="168">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="143">
         <v>4</v>
       </c>
-      <c r="B8" s="179" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="170" t="str">
+      <c r="B8" s="154" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="145" t="str">
         <f>PRORRATEO!A9</f>
         <v>2A</v>
       </c>
-      <c r="D8" s="171" t="str">
+      <c r="D8" s="146" t="str">
         <f>PRORRATEO!B9</f>
         <v>Stagno Jorge Adrian</v>
       </c>
-      <c r="E8" s="180">
+      <c r="E8" s="155">
         <v>5.21</v>
       </c>
-      <c r="F8" s="173">
-        <v>0</v>
-      </c>
-      <c r="G8" s="173">
-        <v>0</v>
-      </c>
-      <c r="H8" s="174">
+      <c r="F8" s="148">
+        <v>0</v>
+      </c>
+      <c r="G8" s="148">
+        <v>0</v>
+      </c>
+      <c r="H8" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="182">
+        <f>J3*E8%</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="175">
+      <c r="L8" s="156">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="210">
-        <f>J3*E8%</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="209">
-        <f>K$3*E8/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="181">
-        <f>G8-F8</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="153"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="168">
+      <c r="M8" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="128"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="143">
         <v>6</v>
       </c>
-      <c r="B9" s="179">
+      <c r="B9" s="154">
         <v>6</v>
       </c>
-      <c r="C9" s="170" t="str">
+      <c r="C9" s="145" t="str">
         <f>PRORRATEO!A10</f>
         <v>2B</v>
       </c>
-      <c r="D9" s="171" t="str">
+      <c r="D9" s="146" t="str">
         <f>PRORRATEO!B10</f>
         <v>Stagno Jorge Adrian</v>
       </c>
-      <c r="E9" s="172">
+      <c r="E9" s="147">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F9" s="173">
-        <v>0</v>
-      </c>
-      <c r="G9" s="173">
-        <v>0</v>
-      </c>
-      <c r="H9" s="174">
+      <c r="F9" s="148">
+        <v>0</v>
+      </c>
+      <c r="G9" s="148">
+        <v>0</v>
+      </c>
+      <c r="H9" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="150">
+        <f>J3*E9%</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="175">
+      <c r="L9" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="175">
-        <f>J3*E9%</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="209">
-        <f>K$3*E9/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="176">
-        <f>G9-F9</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="153"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="168">
+      <c r="M9" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="128"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="143">
         <v>7</v>
       </c>
-      <c r="B10" s="179">
+      <c r="B10" s="154">
         <v>7</v>
       </c>
-      <c r="C10" s="170" t="str">
+      <c r="C10" s="145" t="str">
         <f>PRORRATEO!A11</f>
         <v>2C</v>
       </c>
-      <c r="D10" s="171" t="str">
+      <c r="D10" s="146" t="str">
         <f>PRORRATEO!B11</f>
         <v>Beneyte Lenorado Damian</v>
       </c>
-      <c r="E10" s="172">
+      <c r="E10" s="147">
         <v>5.09</v>
       </c>
-      <c r="F10" s="173">
-        <v>0</v>
-      </c>
-      <c r="G10" s="173">
-        <v>0</v>
-      </c>
-      <c r="H10" s="174">
+      <c r="F10" s="148">
+        <v>0</v>
+      </c>
+      <c r="G10" s="148">
+        <v>0</v>
+      </c>
+      <c r="H10" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="150">
+        <f>J3*E10%</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="175">
+      <c r="L10" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="175">
-        <f>J3*E10%</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="209">
-        <f>K$3*E10/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="176">
-        <f>G10-F10</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="168">
+      <c r="M10" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="143">
         <v>8</v>
       </c>
-      <c r="B11" s="179">
+      <c r="B11" s="154">
         <v>8</v>
       </c>
-      <c r="C11" s="170" t="str">
+      <c r="C11" s="145" t="str">
         <f>PRORRATEO!A12</f>
         <v>3A</v>
       </c>
-      <c r="D11" s="171" t="str">
+      <c r="D11" s="146" t="str">
         <f>PRORRATEO!B12</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E11" s="172">
+      <c r="E11" s="147">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F11" s="173">
-        <v>0</v>
-      </c>
-      <c r="G11" s="173">
-        <v>0</v>
-      </c>
-      <c r="H11" s="174">
+      <c r="F11" s="148">
+        <v>0</v>
+      </c>
+      <c r="G11" s="148">
+        <v>0</v>
+      </c>
+      <c r="H11" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="150">
+        <f>J3*E11%</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="175">
+      <c r="L11" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="175">
-        <f>J3*E11%</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="209">
-        <f>K$3*E11/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="176">
-        <f>G11-F11</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="168">
+      <c r="M11" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="143">
         <v>9</v>
       </c>
-      <c r="B12" s="179">
+      <c r="B12" s="154">
         <v>9</v>
       </c>
-      <c r="C12" s="170" t="str">
+      <c r="C12" s="145" t="str">
         <f>PRORRATEO!A13</f>
         <v>3B</v>
       </c>
-      <c r="D12" s="171" t="str">
+      <c r="D12" s="146" t="str">
         <f>PRORRATEO!B13</f>
         <v>Torres Lilliana Beatriz</v>
       </c>
-      <c r="E12" s="172">
+      <c r="E12" s="147">
         <v>5.09</v>
       </c>
-      <c r="F12" s="173">
-        <v>0</v>
-      </c>
-      <c r="G12" s="173">
-        <v>0</v>
-      </c>
-      <c r="H12" s="174">
+      <c r="F12" s="148">
+        <v>0</v>
+      </c>
+      <c r="G12" s="148">
+        <v>0</v>
+      </c>
+      <c r="H12" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="150">
+        <f>J3*E12%</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="175">
+      <c r="L12" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="175">
-        <f>J3*E12%</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="209">
-        <f>K$3*E12/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="176">
-        <f>G12-F12</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="168">
+      <c r="M12" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="143">
         <v>10</v>
       </c>
-      <c r="B13" s="179">
+      <c r="B13" s="154">
         <v>10</v>
       </c>
-      <c r="C13" s="170" t="str">
+      <c r="C13" s="145" t="str">
         <f>PRORRATEO!A14</f>
         <v>3C</v>
       </c>
-      <c r="D13" s="171" t="str">
+      <c r="D13" s="146" t="str">
         <f>PRORRATEO!B14</f>
         <v>Arostegui Hector/Herrera Monica</v>
       </c>
-      <c r="E13" s="172">
+      <c r="E13" s="147">
         <v>5.04</v>
       </c>
-      <c r="F13" s="173">
-        <v>0</v>
-      </c>
-      <c r="G13" s="173">
-        <v>0</v>
-      </c>
-      <c r="H13" s="174">
+      <c r="F13" s="148">
+        <v>0</v>
+      </c>
+      <c r="G13" s="148">
+        <v>0</v>
+      </c>
+      <c r="H13" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="150">
+        <f>J3*E13%</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="175">
+      <c r="L13" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="175">
-        <f>J3*E13%</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="209">
-        <f>K$3*E13/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="176">
-        <f>G13-F13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="168">
+      <c r="M13" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="143">
         <v>11</v>
       </c>
-      <c r="B14" s="179">
+      <c r="B14" s="154">
         <v>11</v>
       </c>
-      <c r="C14" s="170" t="str">
+      <c r="C14" s="145" t="str">
         <f>PRORRATEO!A15</f>
         <v>4A</v>
       </c>
-      <c r="D14" s="171" t="str">
+      <c r="D14" s="146" t="str">
         <f>PRORRATEO!B15</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E14" s="172">
+      <c r="E14" s="147">
         <v>5.21</v>
       </c>
-      <c r="F14" s="173">
-        <v>0</v>
-      </c>
-      <c r="G14" s="173">
-        <v>0</v>
-      </c>
-      <c r="H14" s="174">
+      <c r="F14" s="148">
+        <v>0</v>
+      </c>
+      <c r="G14" s="148">
+        <v>0</v>
+      </c>
+      <c r="H14" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="150">
+        <f>J3*E14%</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I14" s="175">
+      <c r="L14" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="175">
-        <f>J3*E14%</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="209">
-        <f>K$3*E14/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="176">
-        <f>G14-F14</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="168">
+      <c r="M14" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="143">
         <v>12</v>
       </c>
-      <c r="B15" s="179">
+      <c r="B15" s="154">
         <v>12</v>
       </c>
-      <c r="C15" s="170" t="str">
+      <c r="C15" s="145" t="str">
         <f>PRORRATEO!A16</f>
         <v>4B</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="146" t="str">
         <f>PRORRATEO!B16</f>
         <v>Actis Sofia Magali</v>
       </c>
-      <c r="E15" s="172">
+      <c r="E15" s="147">
         <v>5.1100000000000003</v>
       </c>
-      <c r="F15" s="173">
-        <v>0</v>
-      </c>
-      <c r="G15" s="173">
-        <v>0</v>
-      </c>
-      <c r="H15" s="174">
+      <c r="F15" s="148">
+        <v>0</v>
+      </c>
+      <c r="G15" s="148">
+        <v>0</v>
+      </c>
+      <c r="H15" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="150">
+        <f>J3*E15%</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="175">
+      <c r="L15" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="175">
-        <f>J3*E15%</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="209">
-        <f>K$3*E15/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="176">
-        <f>G15-F15</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="168">
+      <c r="M15" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="143">
         <v>13</v>
       </c>
-      <c r="B16" s="179">
+      <c r="B16" s="154">
         <v>13</v>
       </c>
-      <c r="C16" s="170" t="str">
+      <c r="C16" s="145" t="str">
         <f>PRORRATEO!A17</f>
         <v>4C</v>
       </c>
-      <c r="D16" s="171" t="str">
+      <c r="D16" s="146" t="str">
         <f>PRORRATEO!B17</f>
         <v>Alanis Hebert</v>
       </c>
-      <c r="E16" s="172">
+      <c r="E16" s="147">
         <v>5.09</v>
       </c>
-      <c r="F16" s="173">
-        <v>0</v>
-      </c>
-      <c r="G16" s="173">
-        <v>0</v>
-      </c>
-      <c r="H16" s="174">
+      <c r="F16" s="148">
+        <v>0</v>
+      </c>
+      <c r="G16" s="148">
+        <v>0</v>
+      </c>
+      <c r="H16" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="150">
+        <f>J3*E16%</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="175">
+      <c r="L16" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="175">
-        <f>J3*E16%</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="209">
-        <f>K$3*E16/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="176">
-        <f>G16-F16</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="168">
+      <c r="M16" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="143">
         <v>14</v>
       </c>
-      <c r="B17" s="179">
+      <c r="B17" s="154">
         <v>14</v>
       </c>
-      <c r="C17" s="170" t="str">
+      <c r="C17" s="145" t="str">
         <f>PRORRATEO!A18</f>
         <v>5A</v>
       </c>
-      <c r="D17" s="171" t="str">
+      <c r="D17" s="146" t="str">
         <f>PRORRATEO!B18</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E17" s="172">
+      <c r="E17" s="147">
         <v>5.04</v>
       </c>
-      <c r="F17" s="173">
-        <v>0</v>
-      </c>
-      <c r="G17" s="173">
-        <v>0</v>
-      </c>
-      <c r="H17" s="174">
+      <c r="F17" s="148">
+        <v>0</v>
+      </c>
+      <c r="G17" s="148">
+        <v>0</v>
+      </c>
+      <c r="H17" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="150">
+        <f>J3*E17%</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="175">
+      <c r="L17" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="175">
-        <f>J3*E17%</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="209">
-        <f>K$3*E17/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="176">
-        <f>G17-F17</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="174">
+      <c r="M17" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="143">
+        <v>15</v>
+      </c>
+      <c r="B18" s="154">
+        <v>15</v>
+      </c>
+      <c r="C18" s="145"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="147">
+        <v>5.21</v>
+      </c>
+      <c r="F18" s="148">
+        <v>0</v>
+      </c>
+      <c r="G18" s="148">
+        <v>0</v>
+      </c>
+      <c r="H18" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="168">
-        <v>15</v>
-      </c>
-      <c r="B18" s="179">
-        <v>15</v>
-      </c>
-      <c r="C18" s="170"/>
-      <c r="D18" s="171"/>
-      <c r="E18" s="172">
-        <v>5.21</v>
-      </c>
-      <c r="F18" s="173">
-        <v>0</v>
-      </c>
-      <c r="G18" s="173">
-        <v>0</v>
-      </c>
-      <c r="H18" s="174">
+      <c r="I18" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="150">
+        <f>J3*E18%</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="175">
+      <c r="L18" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="175">
-        <f>J3*E18%</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="209">
-        <f>K$3*E18/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="176">
-        <f>G18-F18</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="168">
+      <c r="M18" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="143">
         <v>16</v>
       </c>
-      <c r="B19" s="179">
+      <c r="B19" s="154">
         <v>16</v>
       </c>
-      <c r="C19" s="170" t="str">
+      <c r="C19" s="145" t="str">
         <f>PRORRATEO!A20</f>
         <v>C1</v>
       </c>
-      <c r="D19" s="171" t="str">
+      <c r="D19" s="146" t="str">
         <f>PRORRATEO!B20</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E19" s="172">
+      <c r="E19" s="147">
         <v>5.04</v>
       </c>
-      <c r="F19" s="173">
-        <v>0</v>
-      </c>
-      <c r="G19" s="173">
-        <v>0</v>
-      </c>
-      <c r="H19" s="174">
+      <c r="F19" s="148">
+        <v>0</v>
+      </c>
+      <c r="G19" s="148">
+        <v>0</v>
+      </c>
+      <c r="H19" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="150">
+        <f>J3*E19%</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="175">
+      <c r="L19" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="175">
-        <f>J3*E19%</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="209">
-        <f>K$3*E19/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="176">
-        <f>G19-F19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="168">
+      <c r="M19" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="143">
         <v>17</v>
       </c>
-      <c r="B20" s="179">
+      <c r="B20" s="154">
         <v>17</v>
       </c>
-      <c r="C20" s="170" t="str">
+      <c r="C20" s="145" t="str">
         <f>PRORRATEO!A21</f>
         <v>C2</v>
       </c>
-      <c r="D20" s="171" t="str">
+      <c r="D20" s="146" t="str">
         <f>PRORRATEO!B21</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E20" s="172">
+      <c r="E20" s="147">
         <v>5.21</v>
       </c>
-      <c r="F20" s="173">
-        <v>0</v>
-      </c>
-      <c r="G20" s="173">
-        <v>0</v>
-      </c>
-      <c r="H20" s="174">
+      <c r="F20" s="148">
+        <v>0</v>
+      </c>
+      <c r="G20" s="148">
+        <v>0</v>
+      </c>
+      <c r="H20" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="150">
+        <f>J3*E20%</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="175">
+      <c r="L20" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="175">
-        <f>J3*E20%</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="209">
-        <f>K$3*E20/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="176">
-        <f>G20-F20</f>
-        <v>0</v>
-      </c>
-      <c r="M20" s="174">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="168">
+      <c r="M20" s="149">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="143">
         <v>18</v>
       </c>
-      <c r="B21" s="179">
+      <c r="B21" s="154">
         <v>18</v>
       </c>
-      <c r="C21" s="170" t="str">
+      <c r="C21" s="145" t="str">
         <f>PRORRATEO!A22</f>
         <v>C3</v>
       </c>
-      <c r="D21" s="171" t="str">
+      <c r="D21" s="146" t="str">
         <f>PRORRATEO!B22</f>
         <v>Torres Lilliana Beatriz</v>
       </c>
-      <c r="E21" s="172">
+      <c r="E21" s="147">
         <v>7.4</v>
       </c>
-      <c r="F21" s="173">
-        <v>0</v>
-      </c>
-      <c r="G21" s="173">
-        <v>0</v>
-      </c>
-      <c r="H21" s="174">
+      <c r="F21" s="148">
+        <v>0</v>
+      </c>
+      <c r="G21" s="148">
+        <v>0</v>
+      </c>
+      <c r="H21" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="150">
+        <f>J3*E21%</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="175">
+      <c r="L21" s="151">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="175">
-        <f>J3*E21%</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="209">
-        <f>K$3*E21/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="176">
-        <f>G21-F21</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="174">
+      <c r="M21" s="149">
         <f>I21+K21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="168">
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="143">
         <v>19</v>
       </c>
-      <c r="B22" s="182">
+      <c r="B22" s="157">
         <v>19</v>
       </c>
-      <c r="C22" s="170" t="str">
+      <c r="C22" s="145" t="str">
         <f>PRORRATEO!A23</f>
         <v>C4</v>
       </c>
-      <c r="D22" s="171" t="str">
+      <c r="D22" s="146" t="str">
         <f>PRORRATEO!B23</f>
         <v>Frosio Diego Martin</v>
       </c>
-      <c r="E22" s="205">
+      <c r="E22" s="178">
         <v>1.08</v>
       </c>
-      <c r="F22" s="173">
-        <v>0</v>
-      </c>
-      <c r="G22" s="173">
-        <v>0</v>
-      </c>
-      <c r="H22" s="174">
+      <c r="F22" s="148">
+        <v>0</v>
+      </c>
+      <c r="G22" s="148">
+        <v>0</v>
+      </c>
+      <c r="H22" s="149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="150"/>
+      <c r="J22" s="150"/>
+      <c r="K22" s="181">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="175"/>
-      <c r="J22" s="175"/>
-      <c r="K22" s="209">
-        <f>K$3*E22/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="176">
-        <v>0</v>
-      </c>
-      <c r="M22" s="174">
-        <f t="shared" ref="M22:M23" si="3">I22+K22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="168">
+      <c r="L22" s="151">
+        <v>0</v>
+      </c>
+      <c r="M22" s="149">
+        <f t="shared" ref="M22:M23" si="5">I22+K22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="143">
         <v>20</v>
       </c>
-      <c r="B23" s="182"/>
-      <c r="C23" s="170" t="str">
+      <c r="B23" s="157"/>
+      <c r="C23" s="145" t="str">
         <f>PRORRATEO!A24</f>
         <v>C5</v>
       </c>
-      <c r="D23" s="171" t="str">
+      <c r="D23" s="146" t="str">
         <f>PRORRATEO!B24</f>
         <v>Sr Propietario</v>
       </c>
-      <c r="E23" s="183">
+      <c r="E23" s="158">
         <v>1.08</v>
       </c>
-      <c r="F23" s="173">
-        <v>0</v>
-      </c>
-      <c r="G23" s="173">
-        <v>0</v>
-      </c>
-      <c r="H23" s="174">
-        <v>0</v>
-      </c>
-      <c r="I23" s="184"/>
-      <c r="J23" s="175"/>
-      <c r="K23" s="209">
-        <f>K$3*E23/Q$7</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="176">
-        <v>0</v>
-      </c>
-      <c r="M23" s="174">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="168">
+      <c r="F23" s="148">
+        <v>0</v>
+      </c>
+      <c r="G23" s="148">
+        <v>0</v>
+      </c>
+      <c r="H23" s="149">
+        <v>0</v>
+      </c>
+      <c r="I23" s="159"/>
+      <c r="J23" s="150"/>
+      <c r="K23" s="181">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="151">
+        <v>0</v>
+      </c>
+      <c r="M23" s="149">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="143">
         <v>24</v>
       </c>
-      <c r="B24" s="182"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="187"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="185"/>
-      <c r="H24" s="186"/>
-      <c r="I24" s="188">
+      <c r="B24" s="157"/>
+      <c r="C24" s="160"/>
+      <c r="D24" s="160"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="160"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="161"/>
+      <c r="I24" s="163">
         <f>SUM(I5:I23)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="208"/>
-      <c r="K24" s="208">
+      <c r="J24" s="180"/>
+      <c r="K24" s="180">
         <f>SUM(K5:K23)</f>
         <v>0</v>
       </c>
-      <c r="L24" s="189"/>
-      <c r="M24" s="186">
+      <c r="L24" s="164"/>
+      <c r="M24" s="161">
         <f>SUM(M5:M23)</f>
         <v>0</v>
       </c>
       <c r="N24" s="39"/>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="152"/>
-      <c r="C25" s="190"/>
-      <c r="D25" s="191"/>
-      <c r="E25" s="192">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="127"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="167">
         <f>SUM(E5:E24)</f>
         <v>91.36</v>
       </c>
-      <c r="F25" s="191"/>
-      <c r="G25" s="191"/>
-      <c r="H25" s="193"/>
-      <c r="I25" s="195"/>
-      <c r="J25" s="194"/>
-      <c r="K25" s="196">
+      <c r="F25" s="166"/>
+      <c r="G25" s="166"/>
+      <c r="H25" s="168"/>
+      <c r="I25" s="170"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="171">
         <f>K24+I24</f>
         <v>0</v>
       </c>
-      <c r="L25" s="193"/>
-      <c r="M25" s="193"/>
-    </row>
-    <row r="26" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="198" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="199"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="148"/>
-      <c r="I26" s="148"/>
-      <c r="J26" s="148"/>
-      <c r="K26" s="148"/>
-      <c r="L26" s="148"/>
-      <c r="M26" s="148"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H27" s="197"/>
-      <c r="I27" s="200"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="200"/>
-      <c r="M27" s="177"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L25" s="168"/>
+      <c r="M25" s="168"/>
+    </row>
+    <row r="26" spans="1:14" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="173" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="222"/>
+      <c r="D26" s="219"/>
+      <c r="E26" s="219"/>
+      <c r="F26" s="219"/>
+      <c r="G26" s="219"/>
+      <c r="H26" s="219"/>
+      <c r="I26" s="219"/>
+      <c r="J26" s="219"/>
+      <c r="K26" s="219"/>
+      <c r="L26" s="219"/>
+      <c r="M26" s="219"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H27" s="172"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="174"/>
+      <c r="M27" s="152"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K30" s="201"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K31" s="200"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E32" s="202"/>
-      <c r="F32" s="202"/>
-      <c r="G32" s="202"/>
-      <c r="H32" s="202"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202"/>
-      <c r="K32" s="203"/>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K30" s="175"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K31" s="174"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="176"/>
+      <c r="K32" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="4">
